--- a/output/Foreign_Assets_Schedule_FA_Yagyank_Chadha_U15172057_AY2026-27.xlsx
+++ b/output/Foreign_Assets_Schedule_FA_Yagyank_Chadha_U15172057_AY2026-27.xlsx
@@ -20,6 +20,8 @@
     <sheet name="FIFO Lots Register" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="CG Summary by Symbol" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Notes for CA" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Capital Gains FY2026-27" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Schedule OS - FY2026-27" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -471,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Table range for VLOOKUP: A4:C26</t>
+          <t>Table range for VLOOKUP: A4:C33</t>
         </is>
       </c>
     </row>
@@ -859,89 +861,249 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>FCY→USD cross rates (IBKR 31-Dec-2025 close — edit if using trade-date FX)</t>
+      <c r="A28" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Units per 1 FCY → USD</t>
+      <c r="A29" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DKK</t>
-        </is>
+      <c r="A30" s="2" t="n">
+        <v>46202</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.15726</v>
+        <v>93.95</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="A31" s="2" t="n">
+        <v>46203</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>1.1746</v>
+        <v>93.95</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
+      <c r="A32" s="2" t="n">
+        <v>46234</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.12849</v>
+        <v>95.2</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
+      <c r="A33" s="2" t="n">
+        <v>46265</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.0063827</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>0.7776049766718507</v>
+        <v>95</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Month-end card — replace with exact SBI card rate if different</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36"/>
+          <t>FCY→USD cross rates (IBKR 31-Dec-2025 close — edit if using trade-date FX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Units per 1 FCY → USD</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1.2615</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CNH</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0.14905</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0.14905</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0.15726</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1.1746</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1.342</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0.12849</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0.0063827</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>0.7776049766718507</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0.031725</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Yellow/input cells on CG sheets: Sale/Cost FCY, Comm USD, FX rates. All P&amp;L columns are formulas.</t>
         </is>
@@ -1115,7 +1277,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="G6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
@@ -1128,7 +1289,6 @@
       <c r="G8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -2711,7 +2871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2842,7 +3002,6 @@
         <v>1563.12</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -2853,6 +3012,529 @@
         <is>
           <t>Detail P&amp;L with editable FX is on 'Capital Gains FY2025-26' (formula-driven). This summary is a static cross-check.</t>
         </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>— FY 2026-27 YTD (to 08-Sep-2026) —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>STCG INR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LTCG INR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Total Gain/(Loss) INR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sale Proceeds USD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2914.T</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>111332</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>111332</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3961.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2463.14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-3867</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-3867</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1109</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1257.95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18113</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18113</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1869.53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1844.91</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-14610</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-14610</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1081.89</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1354.07</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4568.T</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-132717</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-132717</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3288.36</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4635.64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8873</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8873</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1732.26</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1580.02</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>25885</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25885</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1352.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1146.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>34219</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>34219</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F18" t="n">
+        <v>761.62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>403822</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>403822</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9433.620000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5734.07</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BBJP</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7107</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7107</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2821.69</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2744.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BNO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2765</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2561.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2625.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>8202</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8202</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4778.34</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5237.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CNUA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>53936</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>53936</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1684.45</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1247.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>192780</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>192780</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4226.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2445.36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMXC</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>340474</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>340474</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7547.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4452.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>140999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>140999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2531.13</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1158.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-8724</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-8724</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1143.39</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1338.45</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>840612</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>840612</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10919.7</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2217.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-14276</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-14276</v>
+      </c>
+      <c r="E29" t="n">
+        <v>906.09</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1126.48</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>114809</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>114809</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4260</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3332.76</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>47474</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>47474</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4273.23</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4271.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>URA</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1086.72</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1140.04</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +3548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2888,7 +3570,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yagyank Chadha — IBKR U15172057 (Individual) — Advisor: MATCAP WEALTH ADVISORS PRIVATE LIMITED</t>
+          <t>Yagyank Chadha — IBKR U15172057 (Individual) — Advisor: MATCAP WEALTH ADVISORS PRIVATE LIMITED (also spelled Chaddha in some correspondence)</t>
         </is>
       </c>
     </row>
@@ -2931,283 +3613,283 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Annual CY2025 / YE marks</t>
+          <t>FY 2026-27 (partial)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No Calendar-Year Annual furnished. CY2025 synthesized from FY statements. YE2025 closes proxied from 31-Mar-2025 marks where still held, else cost — prefer IBKR Annual / PortfolioAnalyst for filing.</t>
+          <t>Sheets 'Capital Gains FY2026-27' and 'Schedule OS - FY2026-27' cover 01-Apr-2026 to 08-Sep-2026 (statement end). Full-year FY2026-27 requires Activity Statement through 31-Mar-2027. Includes APH 2-for-1 split (03-Sep-2026).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FX</t>
+          <t>Annual CY2025 / YE marks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Non-USD holdings (EUR/HKD/JPY/DKK) converted via IBKR YE cross rates then Rule 115. Editable on FX Lookup / CG sheets.</t>
+          <t>No Calendar-Year Annual furnished. CY2025 synthesized from FY statements. YE2025 closes proxied from 31-Mar-2025 marks where still held, else cost — prefer IBKR Annual / PortfolioAnalyst for filing.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Assessee</t>
+          <t>FX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yagyank Chadha</t>
+          <t>Non-USD holdings (EUR/HKD/JPY/DKK/TWD) converted via IBKR YE/cross rates then Rule 115. Editable on FX Lookup / CG sheets.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Account</t>
+          <t>Assessee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U15172057 — Interactive Brokers LLC (Advisor Client; Advisor: MATCAP WEALTH ADVISORS PRIVATE LIMITED)</t>
+          <t>Yagyank Chadha</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Customer type</t>
+          <t>Account</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>U15172057 — Interactive Brokers LLC (Advisor Client; Advisor: MATCAP WEALTH ADVISORS PRIVATE LIMITED)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Base currency</t>
+          <t>Customer type</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Account funded</t>
+          <t>Base currency</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>First deposit 2024-09-03 (inception statement)</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Schedule FA period</t>
+          <t>Account funded</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calendar Year 2025 (01-Jan-2025 to 31-Dec-2025) — for ITR AY 2026-27</t>
+          <t>First deposit 2024-09-03 (inception statement)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Income / CG period</t>
+          <t>Schedule FA period</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FY 2025-26 (01-Apr-2025 to 31-Mar-2026); also FY 2024-25 sheet for prior year</t>
+          <t>Calendar Year 2025 (01-Jan-2025 to 31-Dec-2025) — for ITR AY 2026-27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Source data</t>
+          <t>Income / CG period</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IBKR Activity Statements: Inception FY2024-25 + Annual CY2025 + Fiscal FY2025-26</t>
+          <t>FY 2025-26 (01-Apr-2025 to 31-Mar-2026); also FY 2024-25 sheet for prior year</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FIFO method</t>
+          <t>Source data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Actual buy dates &amp; IBKR Basis from inception replay; splits (LRCX 10:1, NFLX 10:1) applied</t>
+          <t>IBKR Activity Statements: Inception FY2024-25 + Annual CY2025 + Fiscal FY2025-26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CG reconciliation</t>
+          <t>FIFO method</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sheets 'Capital Gains FY2025-26' / 'FY2024-25' are formula-driven — yellow cells editable; Gain = Sale INR − Comm INR − Cost INR</t>
+          <t>Actual buy dates &amp; IBKR Basis from inception replay; splits (LRCX 10:1, NFLX 10:1) applied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FX Lookup</t>
+          <t>CG reconciliation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Editable SBI TT USD/INR &amp; EUR/INR month-end rates + FCY→USD cross rates</t>
+          <t>Sheets 'Capital Gains FY2025-26' / 'FY2024-25' are formula-driven — yellow cells editable; Gain = Sale INR − Comm INR − Cost INR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Starting NAV CY2025</t>
+          <t>FX Lookup</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USD 121,972.69</t>
+          <t>Editable SBI TT USD/INR &amp; EUR/INR month-end rates + FCY→USD cross rates</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ending NAV CY2025</t>
+          <t>Starting NAV CY2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USD 82,610.66</t>
+          <t>USD 121,972.69</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deposits CY2025</t>
+          <t>Ending NAV CY2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USD 50,000.00</t>
+          <t>USD 82,610.66</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deposits since inception (to 31-Mar-2025)</t>
+          <t>Deposits CY2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USD 62,872.65</t>
+          <t>USD 50,000.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dividends CY2025</t>
+          <t>Deposits since inception (to 31-Mar-2025)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USD 1,617.42 / INR 140,901 (Rule 115)</t>
+          <t>USD 62,872.65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Interest CY2025</t>
+          <t>Dividends CY2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USD 142.47 / INR 12,327 (Rule 115)</t>
+          <t>USD 1,617.42 / INR 140,901 (Rule 115)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dividends FY2025-26</t>
+          <t>Interest CY2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USD 2,054.57 / INR 181,030</t>
+          <t>USD 142.47 / INR 12,327 (Rule 115)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Interest FY2025-26</t>
+          <t>Dividends FY2025-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USD 117.32 / INR 10,166</t>
+          <t>USD 2,054.57 / INR 181,030</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STCG FY2025-26 (INR)</t>
+          <t>Interest FY2025-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-229,701</t>
+          <t>USD 117.32 / INR 10,166</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LTCG FY2025-26 (INR)</t>
+          <t>STCG FY2025-26 (INR)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-229,701</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STCG FY2024-25 (INR)</t>
+          <t>LTCG FY2025-26 (INR)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3219,7 +3901,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LTCG FY2024-25 (INR)</t>
+          <t>STCG FY2024-25 (INR)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3231,133 +3913,4442 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A1 Foreign Bank/Depository</t>
+          <t>LTCG FY2024-25 (INR)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Generally N/A separately — multi-currency cash sits inside IBKR custodial account (A2)</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A2 Custodial Account</t>
+          <t>A1 Foreign Bank/Depository</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Applicable — see sheet; opening: 2024-09-03 (first USD EFT funding)</t>
+          <t>Generally N/A separately — multi-currency cash sits inside IBKR custodial account (A2)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A3 Equity &amp; Debt Interest</t>
+          <t>A2 Custodial Account</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Applicable — 46 FIFO lot lines (one row per acquisition lot; sold lots match Capital Gains)</t>
+          <t>Applicable — see sheet; opening: 2024-09-03 (first USD EFT funding)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A3 Col C (Name of entity)</t>
+          <t>A3 Equity &amp; Debt Interest</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Symbol only (e.g. NOVd, AAPL). Legal name / address remain in Address &amp; Nature columns.</t>
+          <t>Applicable — 46 FIFO lot lines (one row per acquisition lot; sold lots match Capital Gains)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A3 vs CG</t>
+          <t>A3 Col C (Name of entity)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sold lots: A3 Initial = CG Cost (INR), A3 Sale = CG Sale (INR), same Rule 115/EUR FX. Multiple buys (e.g. NOVd 21-Mar &amp; 21-Aug) appear as separate A3 rows.</t>
+          <t>Symbol only (e.g. NOVd, AAPL). Legal name / address remain in Address &amp; Nature columns.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ADR country practice</t>
+          <t>A3 vs CG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
+          <t>Sold lots: A3 Initial = CG Cost (INR), A3 Sale = CG Sale (INR), same Rule 115/EUR FX. Multiple buys (e.g. NOVd 21-Mar &amp; 21-Aug) appear as separate A3 rows.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CPNG</t>
+          <t>ADR country practice</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
+          <t>Underlying issuer country used for ADRs/GDRs (ASML NL, BTI UK, TSM TW, BYDDY CN, HYU KR, RIO UK)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NFLX split</t>
+          <t>CPNG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
+          <t>USA (Delaware corporation, NYSE) despite Korea operations</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LRCX split</t>
+          <t>NFLX split</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
+          <t>10-for-1 split on 14/17-Nov-2025 reflected in FIFO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HYU</t>
+          <t>LRCX split</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+          <t>10-for-1 split on 02/03-Oct-2024 reflected in FIFO (bought 1 pre-split → 10)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>HYU</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cash merger acquisition Jul-2025 — sale proceeds USD 1,339.02 reported as redemption proceeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Action required</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1) Confirm exact SBI TT Buy card rates; 2) Obtain PortfolioAnalyst for true peak NAV; 3) Map withholding to Schedule FSI/TR under DTAA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FY 2026-27 YTD (01-Apr-2026 to 08-Sep-2026) — partial statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dividends FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>USD 825.48 / INR 78,030</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Interest FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>USD 87.88 / INR 8,339</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STCG FY2026-27 YTD (INR)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2,178,508</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LTCG FY2026-27 YTD (INR)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FY2026-27 coverage</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Activity Statement ends 08-Sep-2026 — not full FY. Obtain statement to 31-Mar-2027 for complete year.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capital gains — FY 2026-27 YTD (01-Apr-2026 to 08-Sep-2026). Partial year — statement ends 08-Sep-2026. FIFO. Yellow cells editable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RECONCILIATION SHEET (formula-driven). Gain/(Loss) INR = Sale INR − Comm INR − Cost INR. Holding &gt;730 → LTCG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F=E-D | G=IF(F&gt;730,"LTCG","STCG") | L=H*K | M=I*K | Q=L*N | R=J*P | S=M*O | T=Q-R-S</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>CCY</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Acquisition Date</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Sale Date</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Sale Proceeds (FCY)</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Cost Basis (FCY)</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Comm (USD)</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>FCY→USD Rate</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Sale Proceeds (USD)</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Cost (USD)</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Sale FX Rate</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>Cost FX Rate</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Comm USD/INR Rate</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>Sale (INR)</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>Comm (INR)</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>Cost (INR)</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>Gain/(Loss) INR</t>
+        </is>
+      </c>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F5">
+        <f>E5-D5</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(F5&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1352.3</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1146.1</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f>H5*K5</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>I5*K5</f>
+        <v/>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q5">
+        <f>L5*N5</f>
+        <v/>
+      </c>
+      <c r="R5">
+        <f>J5*P5</f>
+        <v/>
+      </c>
+      <c r="S5">
+        <f>M5*O5</f>
+        <v/>
+      </c>
+      <c r="T5">
+        <f>Q5-R5-S5</f>
+        <v/>
+      </c>
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F6">
+        <f>E6-D6</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF(F6&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>761.62</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <f>H6*K6</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>I6*K6</f>
+        <v/>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q6">
+        <f>L6*N6</f>
+        <v/>
+      </c>
+      <c r="R6">
+        <f>J6*P6</f>
+        <v/>
+      </c>
+      <c r="S6">
+        <f>M6*O6</f>
+        <v/>
+      </c>
+      <c r="T6">
+        <f>Q6-R6-S6</f>
+        <v/>
+      </c>
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F7">
+        <f>E7-D7</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(F7&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1741.8</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1077.73</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <f>H7*K7</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>I7*K7</f>
+        <v/>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q7">
+        <f>L7*N7</f>
+        <v/>
+      </c>
+      <c r="R7">
+        <f>J7*P7</f>
+        <v/>
+      </c>
+      <c r="S7">
+        <f>M7*O7</f>
+        <v/>
+      </c>
+      <c r="T7">
+        <f>Q7-R7-S7</f>
+        <v/>
+      </c>
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F8">
+        <f>E8-D8</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(F8&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>4064.2</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>2514.7</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <f>H8*K8</f>
+        <v/>
+      </c>
+      <c r="M8">
+        <f>I8*K8</f>
+        <v/>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q8">
+        <f>L8*N8</f>
+        <v/>
+      </c>
+      <c r="R8">
+        <f>J8*P8</f>
+        <v/>
+      </c>
+      <c r="S8">
+        <f>M8*O8</f>
+        <v/>
+      </c>
+      <c r="T8">
+        <f>Q8-R8-S8</f>
+        <v/>
+      </c>
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>45568</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F9">
+        <f>E9-D9</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(F9&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1023.93</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1122.41</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <f>H9*K9</f>
+        <v/>
+      </c>
+      <c r="M9">
+        <f>I9*K9</f>
+        <v/>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q9">
+        <f>L9*N9</f>
+        <v/>
+      </c>
+      <c r="R9">
+        <f>J9*P9</f>
+        <v/>
+      </c>
+      <c r="S9">
+        <f>M9*O9</f>
+        <v/>
+      </c>
+      <c r="T9">
+        <f>Q9-R9-S9</f>
+        <v/>
+      </c>
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F10">
+        <f>E10-D10</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>IF(F10&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>3754.41</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>4115.49</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <f>H10*K10</f>
+        <v/>
+      </c>
+      <c r="M10">
+        <f>I10*K10</f>
+        <v/>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q10">
+        <f>L10*N10</f>
+        <v/>
+      </c>
+      <c r="R10">
+        <f>J10*P10</f>
+        <v/>
+      </c>
+      <c r="S10">
+        <f>M10*O10</f>
+        <v/>
+      </c>
+      <c r="T10">
+        <f>Q10-R10-S10</f>
+        <v/>
+      </c>
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F11">
+        <f>E11-D11</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF(F11&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>4273.23</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>4271.5</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <f>H11*K11</f>
+        <v/>
+      </c>
+      <c r="M11">
+        <f>I11*K11</f>
+        <v/>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q11">
+        <f>L11*N11</f>
+        <v/>
+      </c>
+      <c r="R11">
+        <f>J11*P11</f>
+        <v/>
+      </c>
+      <c r="S11">
+        <f>M11*O11</f>
+        <v/>
+      </c>
+      <c r="T11">
+        <f>Q11-R11-S11</f>
+        <v/>
+      </c>
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>URA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F12">
+        <f>E12-D12</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IF(F12&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1086.72</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1140.04</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <f>H12*K12</f>
+        <v/>
+      </c>
+      <c r="M12">
+        <f>I12*K12</f>
+        <v/>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q12">
+        <f>L12*N12</f>
+        <v/>
+      </c>
+      <c r="R12">
+        <f>J12*P12</f>
+        <v/>
+      </c>
+      <c r="S12">
+        <f>M12*O12</f>
+        <v/>
+      </c>
+      <c r="T12">
+        <f>Q12-R12-S12</f>
+        <v/>
+      </c>
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMXC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F13">
+        <f>E13-D13</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF(F13&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>5160</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2968.17</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <f>H13*K13</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>I13*K13</f>
+        <v/>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q13">
+        <f>L13*N13</f>
+        <v/>
+      </c>
+      <c r="R13">
+        <f>J13*P13</f>
+        <v/>
+      </c>
+      <c r="S13">
+        <f>M13*O13</f>
+        <v/>
+      </c>
+      <c r="T13">
+        <f>Q13-R13-S13</f>
+        <v/>
+      </c>
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F14">
+        <f>E14-D14</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF(F14&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1278</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>999.83</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <f>H14*K14</f>
+        <v/>
+      </c>
+      <c r="M14">
+        <f>I14*K14</f>
+        <v/>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q14">
+        <f>L14*N14</f>
+        <v/>
+      </c>
+      <c r="R14">
+        <f>J14*P14</f>
+        <v/>
+      </c>
+      <c r="S14">
+        <f>M14*O14</f>
+        <v/>
+      </c>
+      <c r="T14">
+        <f>Q14-R14-S14</f>
+        <v/>
+      </c>
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F15">
+        <f>E15-D15</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF(F15&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2982</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>2332.93</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <f>H15*K15</f>
+        <v/>
+      </c>
+      <c r="M15">
+        <f>I15*K15</f>
+        <v/>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q15">
+        <f>L15*N15</f>
+        <v/>
+      </c>
+      <c r="R15">
+        <f>J15*P15</f>
+        <v/>
+      </c>
+      <c r="S15">
+        <f>M15*O15</f>
+        <v/>
+      </c>
+      <c r="T15">
+        <f>Q15-R15-S15</f>
+        <v/>
+      </c>
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4568.T</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F16">
+        <f>E16-D16</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IF(F16&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>257600</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>363140.28</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>206.08</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.0063827</v>
+      </c>
+      <c r="L16">
+        <f>H16*K16</f>
+        <v/>
+      </c>
+      <c r="M16">
+        <f>I16*K16</f>
+        <v/>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q16">
+        <f>L16*N16</f>
+        <v/>
+      </c>
+      <c r="R16">
+        <f>J16*P16</f>
+        <v/>
+      </c>
+      <c r="S16">
+        <f>M16*O16</f>
+        <v/>
+      </c>
+      <c r="T16">
+        <f>Q16-R16-S16</f>
+        <v/>
+      </c>
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4568.T</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F17">
+        <f>E17-D17</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>IF(F17&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>257600</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>363140.28</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>206.08</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.0063827</v>
+      </c>
+      <c r="L17">
+        <f>H17*K17</f>
+        <v/>
+      </c>
+      <c r="M17">
+        <f>I17*K17</f>
+        <v/>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q17">
+        <f>L17*N17</f>
+        <v/>
+      </c>
+      <c r="R17">
+        <f>J17*P17</f>
+        <v/>
+      </c>
+      <c r="S17">
+        <f>M17*O17</f>
+        <v/>
+      </c>
+      <c r="T17">
+        <f>Q17-R17-S17</f>
+        <v/>
+      </c>
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F18">
+        <f>E18-D18</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF(F18&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>271400</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>247547.88</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>217.12</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.0063827</v>
+      </c>
+      <c r="L18">
+        <f>H18*K18</f>
+        <v/>
+      </c>
+      <c r="M18">
+        <f>I18*K18</f>
+        <v/>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q18">
+        <f>L18*N18</f>
+        <v/>
+      </c>
+      <c r="R18">
+        <f>J18*P18</f>
+        <v/>
+      </c>
+      <c r="S18">
+        <f>M18*O18</f>
+        <v/>
+      </c>
+      <c r="T18">
+        <f>Q18-R18-S18</f>
+        <v/>
+      </c>
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>700</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F19">
+        <f>E19-D19</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF(F19&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>8631</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>9790.280000000001</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.12849</v>
+      </c>
+      <c r="L19">
+        <f>H19*K19</f>
+        <v/>
+      </c>
+      <c r="M19">
+        <f>I19*K19</f>
+        <v/>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q19">
+        <f>L19*N19</f>
+        <v/>
+      </c>
+      <c r="R19">
+        <f>J19*P19</f>
+        <v/>
+      </c>
+      <c r="S19">
+        <f>M19*O19</f>
+        <v/>
+      </c>
+      <c r="T19">
+        <f>Q19-R19-S19</f>
+        <v/>
+      </c>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>500</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F20">
+        <f>E20-D20</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(F20&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>14550</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>14358.41</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.12849</v>
+      </c>
+      <c r="L20">
+        <f>H20*K20</f>
+        <v/>
+      </c>
+      <c r="M20">
+        <f>I20*K20</f>
+        <v/>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q20">
+        <f>L20*N20</f>
+        <v/>
+      </c>
+      <c r="R20">
+        <f>J20*P20</f>
+        <v/>
+      </c>
+      <c r="S20">
+        <f>M20*O20</f>
+        <v/>
+      </c>
+      <c r="T20">
+        <f>Q20-R20-S20</f>
+        <v/>
+      </c>
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="F21">
+        <f>E21-D21</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF(F21&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>8420</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>10538.3</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.12849</v>
+      </c>
+      <c r="L21">
+        <f>H21*K21</f>
+        <v/>
+      </c>
+      <c r="M21">
+        <f>I21*K21</f>
+        <v/>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="Q21">
+        <f>L21*N21</f>
+        <v/>
+      </c>
+      <c r="R21">
+        <f>J21*P21</f>
+        <v/>
+      </c>
+      <c r="S21">
+        <f>M21*O21</f>
+        <v/>
+      </c>
+      <c r="T21">
+        <f>Q21-R21-S21</f>
+        <v/>
+      </c>
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CNUA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F22">
+        <f>E22-D22</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(F22&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1434.06</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>1062.15</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <f>H22*K22</f>
+        <v/>
+      </c>
+      <c r="M22">
+        <f>I22*K22</f>
+        <v/>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q22">
+        <f>L22*N22</f>
+        <v/>
+      </c>
+      <c r="R22">
+        <f>J22*P22</f>
+        <v/>
+      </c>
+      <c r="S22">
+        <f>M22*O22</f>
+        <v/>
+      </c>
+      <c r="T22">
+        <f>Q22-R22-S22</f>
+        <v/>
+      </c>
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>62</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F23">
+        <f>E23-D23</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IF(F23&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>3627.62</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2141.64</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <f>H23*K23</f>
+        <v/>
+      </c>
+      <c r="M23">
+        <f>I23*K23</f>
+        <v/>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q23">
+        <f>L23*N23</f>
+        <v/>
+      </c>
+      <c r="R23">
+        <f>J23*P23</f>
+        <v/>
+      </c>
+      <c r="S23">
+        <f>M23*O23</f>
+        <v/>
+      </c>
+      <c r="T23">
+        <f>Q23-R23-S23</f>
+        <v/>
+      </c>
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F24">
+        <f>E24-D24</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF(F24&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2531.13</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>1158.1</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <f>H24*K24</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>I24*K24</f>
+        <v/>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q24">
+        <f>L24*N24</f>
+        <v/>
+      </c>
+      <c r="R24">
+        <f>J24*P24</f>
+        <v/>
+      </c>
+      <c r="S24">
+        <f>M24*O24</f>
+        <v/>
+      </c>
+      <c r="T24">
+        <f>Q24-R24-S24</f>
+        <v/>
+      </c>
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F25">
+        <f>E25-D25</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF(F25&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>10919.7</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2217.7</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <f>H25*K25</f>
+        <v/>
+      </c>
+      <c r="M25">
+        <f>I25*K25</f>
+        <v/>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q25">
+        <f>L25*N25</f>
+        <v/>
+      </c>
+      <c r="R25">
+        <f>J25*P25</f>
+        <v/>
+      </c>
+      <c r="S25">
+        <f>M25*O25</f>
+        <v/>
+      </c>
+      <c r="T25">
+        <f>Q25-R25-S25</f>
+        <v/>
+      </c>
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2914.T</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>45725</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="F26">
+        <f>E26-D26</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>IF(F26&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>620600</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>385908.48</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>496.48</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.0063827</v>
+      </c>
+      <c r="L26">
+        <f>H26*K26</f>
+        <v/>
+      </c>
+      <c r="M26">
+        <f>I26*K26</f>
+        <v/>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q26">
+        <f>L26*N26</f>
+        <v/>
+      </c>
+      <c r="R26">
+        <f>J26*P26</f>
+        <v/>
+      </c>
+      <c r="S26">
+        <f>M26*O26</f>
+        <v/>
+      </c>
+      <c r="T26">
+        <f>Q26-R26-S26</f>
+        <v/>
+      </c>
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F27">
+        <f>E27-D27</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IF(F27&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>4226.4</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>2445.36</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <f>H27*K27</f>
+        <v/>
+      </c>
+      <c r="M27">
+        <f>I27*K27</f>
+        <v/>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q27">
+        <f>L27*N27</f>
+        <v/>
+      </c>
+      <c r="R27">
+        <f>J27*P27</f>
+        <v/>
+      </c>
+      <c r="S27">
+        <f>M27*O27</f>
+        <v/>
+      </c>
+      <c r="T27">
+        <f>Q27-R27-S27</f>
+        <v/>
+      </c>
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EMXC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>45541</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F28">
+        <f>E28-D28</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>IF(F28&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>2387.5</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>1484.08</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <f>H28*K28</f>
+        <v/>
+      </c>
+      <c r="M28">
+        <f>I28*K28</f>
+        <v/>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q28">
+        <f>L28*N28</f>
+        <v/>
+      </c>
+      <c r="R28">
+        <f>J28*P28</f>
+        <v/>
+      </c>
+      <c r="S28">
+        <f>M28*O28</f>
+        <v/>
+      </c>
+      <c r="T28">
+        <f>Q28-R28-S28</f>
+        <v/>
+      </c>
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BNO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="F29">
+        <f>E29-D29</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>IF(F29&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>2561.5</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>2625.75</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <f>H29*K29</f>
+        <v/>
+      </c>
+      <c r="M29">
+        <f>I29*K29</f>
+        <v/>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>90.56</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q29">
+        <f>L29*N29</f>
+        <v/>
+      </c>
+      <c r="R29">
+        <f>J29*P29</f>
+        <v/>
+      </c>
+      <c r="S29">
+        <f>M29*O29</f>
+        <v/>
+      </c>
+      <c r="T29">
+        <f>Q29-R29-S29</f>
+        <v/>
+      </c>
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BBJP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>38</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F30">
+        <f>E30-D30</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF(F30&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>2821.69</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>2744.98</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <f>H30*K30</f>
+        <v/>
+      </c>
+      <c r="M30">
+        <f>I30*K30</f>
+        <v/>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="Q30">
+        <f>L30*N30</f>
+        <v/>
+      </c>
+      <c r="R30">
+        <f>J30*P30</f>
+        <v/>
+      </c>
+      <c r="S30">
+        <f>M30*O30</f>
+        <v/>
+      </c>
+      <c r="T30">
+        <f>Q30-R30-S30</f>
+        <v/>
+      </c>
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F31">
+        <f>E31-D31</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>IF(F31&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>438.36</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>563.24</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <f>H31*K31</f>
+        <v/>
+      </c>
+      <c r="M31">
+        <f>I31*K31</f>
+        <v/>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Q31">
+        <f>L31*N31</f>
+        <v/>
+      </c>
+      <c r="R31">
+        <f>J31*P31</f>
+        <v/>
+      </c>
+      <c r="S31">
+        <f>M31*O31</f>
+        <v/>
+      </c>
+      <c r="T31">
+        <f>Q31-R31-S31</f>
+        <v/>
+      </c>
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="F32">
+        <f>E32-D32</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF(F32&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>454.2</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>535.38</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <f>H32*K32</f>
+        <v/>
+      </c>
+      <c r="M32">
+        <f>I32*K32</f>
+        <v/>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Q32">
+        <f>L32*N32</f>
+        <v/>
+      </c>
+      <c r="R32">
+        <f>J32*P32</f>
+        <v/>
+      </c>
+      <c r="S32">
+        <f>M32*O32</f>
+        <v/>
+      </c>
+      <c r="T32">
+        <f>Q32-R32-S32</f>
+        <v/>
+      </c>
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F33">
+        <f>E33-D33</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>IF(F33&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>281.62</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <f>H33*K33</f>
+        <v/>
+      </c>
+      <c r="M33">
+        <f>I33*K33</f>
+        <v/>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Q33">
+        <f>L33*N33</f>
+        <v/>
+      </c>
+      <c r="R33">
+        <f>J33*P33</f>
+        <v/>
+      </c>
+      <c r="S33">
+        <f>M33*O33</f>
+        <v/>
+      </c>
+      <c r="T33">
+        <f>Q33-R33-S33</f>
+        <v/>
+      </c>
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="F34">
+        <f>E34-D34</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IF(F34&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>689.1900000000001</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>803.0700000000001</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <f>H34*K34</f>
+        <v/>
+      </c>
+      <c r="M34">
+        <f>I34*K34</f>
+        <v/>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Q34">
+        <f>L34*N34</f>
+        <v/>
+      </c>
+      <c r="R34">
+        <f>J34*P34</f>
+        <v/>
+      </c>
+      <c r="S34">
+        <f>M34*O34</f>
+        <v/>
+      </c>
+      <c r="T34">
+        <f>Q34-R34-S34</f>
+        <v/>
+      </c>
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F35">
+        <f>E35-D35</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>IF(F35&gt;730,"LTCG","STCG")</f>
+        <v/>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>242.43</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>281.62</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <f>H35*K35</f>
+        <v/>
+      </c>
+      <c r="M35">
+        <f>I35*K35</f>
+        <v/>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q35">
+        <f>L35*N35</f>
+        <v/>
+      </c>
+      <c r="R35">
+        <f>J35*P35</f>
+        <v/>
+      </c>
+      <c r="S35">
+        <f>M35*O35</f>
+        <v/>
+      </c>
+      <c r="T35">
+        <f>Q35-R35-S35</f>
+        <v/>
+      </c>
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL STCG (INR)</t>
+        </is>
+      </c>
+      <c r="T37" s="4">
+        <f>SUMIF(G5:G35,"STCG",T5:T35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL LTCG (INR)</t>
+        </is>
+      </c>
+      <c r="T38" s="4">
+        <f>SUMIF(G5:G35,"LTCG",T5:T35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL CG (INR)</t>
+        </is>
+      </c>
+      <c r="T39" s="4">
+        <f>T37+T38</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A2:U2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Interest &amp; Dividend income — FY 2026-27 YTD (01-Apr-2026 to 08-Sep-2026). Partial — full year needs statement through 31-Mar-2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Amount (FCY)</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Amount (USD)</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>USD/INR (Rule 115)</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Amount (INR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>— INTEREST —</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EUR IBKR Managed Securities (SYEP) for May-2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.2568</v>
+      </c>
+      <c r="F4" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EUR IBKR Managed Securities (SYEP) for Jun-2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.2568</v>
+      </c>
+      <c r="F5" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EUR IBKR Managed Securities (SYEP) for Jul-2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.0454</v>
+      </c>
+      <c r="F6" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EUR IBKR Managed Securities (SYEP) for Aug-2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="F7" t="n">
+        <v>95</v>
+      </c>
+      <c r="G7" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HKD IBKR Managed Securities (SYEP) for Mar-2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.2271</v>
+      </c>
+      <c r="F8" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HKD IBKR Managed Securities (SYEP) for Apr-2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.0366</v>
+      </c>
+      <c r="F9" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HKD IBKR Managed Securities (SYEP) for May-2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="F10" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HKD IBKR Managed Securities (SYEP) for Jun-2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.2566</v>
+      </c>
+      <c r="F11" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JPY IBKR Managed Securities (SYEP) for Jul-2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="F12" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JPY IBKR Managed Securities (SYEP) for Aug-2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>95</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>95</v>
+      </c>
+      <c r="G13" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>USD IBKR Managed Securities (SYEP) for Mar-2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F14" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>USD Debit Interest for Apr-2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F15" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>USD IBKR Managed Securities (SYEP) for Apr-2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>USD Debit Interest for May-2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F17" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>USD IBKR Managed Securities (SYEP) for May-2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F18" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>USD Credit Interest for Jun-2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F19" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>USD Debit Interest for Jun-2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F20" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>USD IBKR Managed Securities (SYEP) for Jun-2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G21" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>USD Credit Interest for Jul-2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="E22" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F22" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>USD IBKR Managed Securities (SYEP) for Jul-2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F23" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>USD Credit Interest for Aug-2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="F24" t="n">
+        <v>95</v>
+      </c>
+      <c r="G24" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>USD IBKR Managed Securities (SYEP) for Aug-2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="F25" t="n">
+        <v>95</v>
+      </c>
+      <c r="G25" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TOTAL INTEREST</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>87.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8339</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>— DIVIDENDS —</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NOVO B(DK0062498333) Cash Dividend DKK 3.75 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.6918</v>
+      </c>
+      <c r="F29" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SHELL.DvR(NL00150743A0) Expire Dividend Right (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="E30" t="n">
+        <v>77.042</v>
+      </c>
+      <c r="F30" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7288</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3416(HK0000978954) Cash Dividend HKD 0.14 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>140</v>
+      </c>
+      <c r="E31" t="n">
+        <v>17.9886</v>
+      </c>
+      <c r="F31" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3416(HK0000978954) Cash Dividend HKD 0.14 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>140</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.9886</v>
+      </c>
+      <c r="F32" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3416(HK0000978954) Cash Dividend HKD 0.15 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E33" t="n">
+        <v>19.2735</v>
+      </c>
+      <c r="F33" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7203.T(JP3633400001) Cash Dividend JPY 50 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31.9135</v>
+      </c>
+      <c r="F34" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4568.T(JP3475350009) Cash Dividend JPY 39 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E35" t="n">
+        <v>49.7851</v>
+      </c>
+      <c r="F35" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2914.T(JP3726800000) Cash Dividend JPY 136 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E36" t="n">
+        <v>86.8047</v>
+      </c>
+      <c r="F36" t="n">
+        <v>95</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8246</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2890(TW0002890001) Cash Dividend TWD 1.1 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>660</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20.9385</v>
+      </c>
+      <c r="F37" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LRCX(US5128073062) Cash Dividend USD 0.26 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TSM(US8740391003) Cash Dividend USD 0.938972 per Share (Ordinary Div - NRA Withholding Exempt)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="F39" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CSCO(US17275R1023) Cash Dividend USD 0.42 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46139</v>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1) Confirm exact SBI TT Buy card rates; 2) Obtain PortfolioAnalyst for true peak NAV; 3) Map withholding to Schedule FSI/TR under DTAA.</t>
-        </is>
+          <t>GE(US3696043013) Cash Dividend USD 0.47 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F41" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ASML(USN070592100) Cash Dividend USD 3.16845 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="F42" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TIP(US4642871762) Cash Dividend USD 0.560849 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="E43" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="F43" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AXP(US0258161092) Cash Dividend USD 0.95 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F44" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BX(US09260D1072) Cash Dividend USD 1.16 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="E45" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F45" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4619</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CAT(US1491231015) Cash Dividend USD 1.51 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F46" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TGT(US87612E1064) Cash Dividend USD 1.14 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TIP(US4642871762) Cash Dividend USD 1.277516 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E48" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="F48" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4713</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AEP(US0255371017) Cash Dividend USD 0.95 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G49" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IBM(US4592001014) Cash Dividend USD 1.69 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F50" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G50" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LLY(US5324571083) Cash Dividend USD 1.73 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="F51" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G51" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MSFT(US5949181045) Cash Dividend USD 0.91 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F52" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>EMXC(US46434G7640) Payment in Lieu of Dividend (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BAC(US0605051046) Cash Dividend USD 0.28 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="E54" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F54" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4291</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DXJ(US97717W8516) Payment in Lieu of Dividend (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="E55" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="F55" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DXJ(US97717W8516) Cash Dividend USD 1.155 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G56" t="n">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AVGO(US11135F1012) Cash Dividend USD 0.65 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="F57" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="G57" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LRCX(US5128073062) Cash Dividend USD 0.26 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G58" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TSM(US8740391003) Cash Dividend USD 0.939325 per Share (Ordinary Div - NRA Withholding Exempt)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="E59" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="F59" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CSCO(US17275R1023) Cash Dividend USD 0.42 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G60" t="n">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GE(US3696043013) Cash Dividend USD 0.47 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F61" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G61" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JPM(US46625H1005) Cash Dividend USD 1.50 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>9</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="G62" t="n">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ASML(USN070592100) Cash Dividend USD 2.137748 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="E63" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F63" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DHI(US23331A1097) Cash Dividend USD 0.45 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="F64" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CAT(US1491231015) Cash Dividend USD 1.63 per Share (Ordinary Dividend)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="F65" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TOTAL DIVIDENDS</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>825.48</v>
+      </c>
+      <c r="G66" t="n">
+        <v>78030</v>
       </c>
     </row>
   </sheetData>
@@ -3457,7 +8448,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="n">
         <v>1</v>
@@ -3515,7 +8505,6 @@
           <t>Xiaomi Corporation, Cayman Islands / Beijing ops</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Listed Foreign Equity Share (Company)</t>
@@ -3561,7 +8550,6 @@
           <t>Xiaomi Corporation, Cayman Islands / Beijing ops</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Listed Foreign Equity Share (Company)</t>
@@ -3657,7 +8645,6 @@
           <t>ChinaAMC, Hong Kong</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Exchange Traded Fund (Investment Trust)</t>
@@ -3703,7 +8690,6 @@
           <t>Global X ETFs / Mirae Asset, Hong Kong</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Exchange Traded Fund (Investment Trust)</t>
@@ -3749,7 +8735,6 @@
           <t>Global X ETFs / Mirae Asset, Hong Kong</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Exchange Traded Fund (Investment Trust)</t>
@@ -5090,8 +10075,6 @@
           <t>NOV</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Listed Foreign Equity / ETF</t>
@@ -5768,7 +10751,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="G52" t="inlineStr">
         <is>
@@ -8285,7 +13267,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -8434,7 +13415,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -8583,7 +13563,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -8652,7 +13631,6 @@
         <v>153229</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -9511,7 +14489,6 @@
         <v>12327</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -12913,7 +17890,6 @@
         <v>10166</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -15564,7 +20540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -22056,6 +27032,1062 @@
       </c>
       <c r="H203" t="n">
         <v>-132</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>NOVO B(DK0062498333) Cash Dividend DKK 3.75 per Share - DK Tax</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>-30.37</v>
+      </c>
+      <c r="F204" t="n">
+        <v>-4.776</v>
+      </c>
+      <c r="G204" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H204" t="n">
+        <v>-455</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>7203.T(JP3633400001) Cash Dividend JPY 50 per Share - JP Tax</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>-766</v>
+      </c>
+      <c r="F205" t="n">
+        <v>-4.8891</v>
+      </c>
+      <c r="G205" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H205" t="n">
+        <v>-463</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4568.T(JP3475350009) Cash Dividend JPY 39 per Share - JP Tax</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>-1195</v>
+      </c>
+      <c r="F206" t="n">
+        <v>-7.6273</v>
+      </c>
+      <c r="G206" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H206" t="n">
+        <v>-722</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2914.T(JP3726800000) Cash Dividend JPY 136 per Share - JP Tax</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>-2083</v>
+      </c>
+      <c r="F207" t="n">
+        <v>-13.2952</v>
+      </c>
+      <c r="G207" t="n">
+        <v>95</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-1263</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2890(TW0002890001) Cash Dividend TWD 1.1 per Share - TW Tax</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>-138.6</v>
+      </c>
+      <c r="F208" t="n">
+        <v>-4.3971</v>
+      </c>
+      <c r="G208" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H208" t="n">
+        <v>-419</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>LRCX(US5128073062) Cash Dividend USD 0.26 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="F209" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="G209" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-182</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>TSM(US8740391003) Cash Dividend USD 0.938972 per Share - TW Tax</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="F210" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="G210" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-826</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CSCO(US17275R1023) Cash Dividend USD 0.42 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G211" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-196</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>GE(US3696043013) Cash Dividend USD 0.47 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="F212" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="G212" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="H212" t="n">
+        <v>-76</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ASML(USN070592100) Cash Dividend USD 3.16845 per Share - NL Tax</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="F213" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="G213" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H213" t="n">
+        <v>-270</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>TIP(US4642871762) Cash Dividend USD 0.560849 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="F214" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="G214" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H214" t="n">
+        <v>-519</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>AXP(US0258161092) Cash Dividend USD 0.95 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F215" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G215" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H215" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>BX(US09260D1072) Cash Dividend USD 1.16 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="F216" t="n">
+        <v>-12.18</v>
+      </c>
+      <c r="G216" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H216" t="n">
+        <v>-1155</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>CAT(US1491231015) Cash Dividend USD 1.51 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="F217" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="G217" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H217" t="n">
+        <v>-107</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>TGT(US87612E1064) Cash Dividend USD 1.14 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="F218" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="G218" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H218" t="n">
+        <v>-809</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TIP(US4642871762) Cash Dividend USD 1.277516 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="F219" t="n">
+        <v>-12.46</v>
+      </c>
+      <c r="G219" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H219" t="n">
+        <v>-1179</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>AEP(US0255371017) Cash Dividend USD 0.95 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="F220" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="G220" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-225</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>IBM(US4592001014) Cash Dividend USD 1.69 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="F221" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="G221" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H221" t="n">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>LLY(US5324571083) Cash Dividend USD 1.73 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F222" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G222" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-123</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>MSFT(US5949181045) Cash Dividend USD 0.91 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="F223" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G223" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>EMXC(US46434G7640) Payment in Lieu of Dividend - US Tax</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="F224" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="G224" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-1043</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>BAC(US0605051046) Cash Dividend USD 0.28 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="F225" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G225" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-1073</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>DXJ(US97717W8516) Payment in Lieu of Dividend - US Tax</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="F226" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="G226" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H226" t="n">
+        <v>-437</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>DXJ(US97717W8516) Cash Dividend USD 1.155 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="F227" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="G227" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H227" t="n">
+        <v>-219</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>AVGO(US11135F1012) Cash Dividend USD 0.65 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="F228" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="G228" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-138</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>LRCX(US5128073062) Cash Dividend USD 0.26 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="F229" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="G229" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-183</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TSM(US8740391003) Cash Dividend USD 0.939325 per Share - TW Tax</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="F230" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="G230" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="H230" t="n">
+        <v>-834</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>CSCO(US17275R1023) Cash Dividend USD 0.42 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="F231" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G231" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="H231" t="n">
+        <v>-197</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>GE(US3696043013) Cash Dividend USD 0.47 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="F232" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="G232" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>JPM(US46625H1005) Cash Dividend USD 1.50 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="F233" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="G233" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="H233" t="n">
+        <v>-211</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ASML(USN070592100) Cash Dividend USD 2.137748 per Share - NL Tax</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="F234" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="G234" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H234" t="n">
+        <v>-183</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>DHI(US23331A1097) Cash Dividend USD 0.45 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F235" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="G235" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-142</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>FY2026-27 YTD</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>CAT(US1491231015) Cash Dividend USD 1.63 per Share - US Tax</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="F236" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="G236" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="H236" t="n">
+        <v>-116</v>
       </c>
     </row>
   </sheetData>
@@ -22296,7 +28328,6 @@
         <f>Q5-R5-S5</f>
         <v/>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22529,7 +28560,6 @@
         <f>Q8-R8-S8</f>
         <v/>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22689,7 +28719,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="G12" s="4" t="inlineStr">
         <is>
@@ -22723,7 +28752,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
